--- a/MAJSushiConfig/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-allergy-intolerance-document.xlsx
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-allergy-intolerance-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-allergy-intolerance-document</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -691,7 +691,7 @@
     <t>AllergyIntolerance.type.extension.value[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-allergy-intolerance-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-allergy-intolerance-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -788,7 +788,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-allergy-code|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-allergy-code|0.1.0</t>
   </si>
   <si>
     <t>substance/product:@@ -817,7 +817,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -1120,7 +1120,7 @@
     <t>Coding of the specific substance (or pharmaceutical product) with a terminology capable of triggering decision support should be used wherever possible.  The 'code' element allows for the use of a specific substance or pharmaceutical product, or a group or class of substances. In the case of an allergy or intolerance to a class of substances, (for example, "penicillins"), the 'reaction.substance' element could be used to code the specific substance that was identified as having caused the reaction (for example, "amoxycillin"). Duplication of the value in the 'code' and 'reaction.substance' elements is acceptable when a specific substance has been recorded in 'code'.</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-allergy-substance|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-allergy-substance|0.1.0</t>
   </si>
   <si>
     <t>outBoundRelationship[typeCode=SAS].target[classCode=SBADM, code &lt;= ExposureCode].participation[typeCode=CSM].role[classCode=ADMM].player[classCode=MAT, determinerCode=KIND, code &lt;= ExposureAgentEntityType]</t>
@@ -1563,7 +1563,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="174.21484375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="167.8125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1578,7 +1578,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.9140625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.71484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
